--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8704,7 +8704,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -8712,7 +8712,7 @@
           <t>B | 1684呎 (4+房)
 $9730万
 $57,779/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -8781,7 +8781,7 @@
           <t>B | 1684呎 (4+房)
 $9750万
 $57,898/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
           <t>A | 1679呎 (4+房)
 $9200万
 $54,795/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8804,7 +8804,7 @@
           <t>B | 1684呎 (4+房)
 $9120万
 $54,157/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
           <t>A | 1679呎 (4+房)
 $8642万
 $51,471/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8827,7 +8827,7 @@
           <t>B | 1684呎 (4+房)
 $8642万
 $51,318/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
           <t>A | 1679呎 (4+房)
 $8478万
 $50,494/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8850,7 +8850,7 @@
           <t>B | 1684呎 (4+房)
 $8478万
 $50,344/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
           <t>A | 1679呎 (4+房)
 $8305万
 $49,464/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -8957,7 +8957,7 @@
           <t>A | 1679呎 (4+房)
 $7960万
 $47,409/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -8965,7 +8965,7 @@
           <t>B | 1686呎 (4+房)
 $7960万
 $47,212/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
           <t>A | 1679呎 (4+房)
 $8280万
 $49,315/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -8988,7 +8988,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
           <t>A | 1679呎 (4+房)
 $8120万
 $48,362/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9011,7 +9011,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
           <t>A | 687呎 (2房)
 $2714万
 $39,500/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9255,7 +9255,7 @@
           <t>C | 710呎 (2房)
 $3300万
 $46,479/呎
-(26年-07月-02日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -9286,7 +9286,7 @@
           <t>A | 687呎 (2房)
 $2670万
 $38,865/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9294,7 +9294,7 @@
           <t>B | 645呎 (2房)
 $2489万
 $38,589/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9302,7 +9302,7 @@
           <t>C | 710呎 (2房)
 $2750万
 $38,732/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9318,7 +9318,7 @@
           <t>E | 439呎 (2房)
 $2041万
 $46,492/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
           <t>A | 687呎 (2房)
 $2638万
 $38,400/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 645呎 (2房)
 $2454万
 $38,043/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 710呎 (2房)
 $2700万
 $38,028/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>A | 687呎 (2房)
 $2615万
 $38,065/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>B | 645呎 (2房)
 $2436万
 $37,775/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>C | 710呎 (2房)
 $2682万
 $37,778/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>D | 434呎 (2房)
 $1988万
 $45,810/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>E | 439呎 (2房)
 $2047万
 $46,622/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
           <t>A | 687呎 (2房)
 $2563万
 $37,300/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>C | 710呎 (2房)
 $2640万
 $37,180/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9459,7 +9459,7 @@
           <t>E | 439呎 (2房)
 $2030万
 $46,241/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
           <t>A | 687呎 (2房)
 $3010万
 $43,814/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9490,7 +9490,7 @@
           <t>C | 710呎 (2房)
 $2980万
 $41,972/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>E | 439呎 (2房)
 $2319万
 $52,832/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
           <t>A | 687呎 (2房)
 $2961万
 $43,100/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9945,7 +9945,7 @@
           <t>B | 622呎 (2房)
 $2288万
 $36,785/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,12 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +283,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1840,7 +1849,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1850,12 +1859,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1865,12 +1874,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1880,7 +1889,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1919,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1920,12 +1929,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1935,12 +1944,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1950,7 +1959,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8620,14 +8629,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>19</t>
@@ -8635,7 +8644,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8860,20 +8869,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 1679呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,12 +131,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,9 +277,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1849,7 +1840,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1859,12 +1850,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1874,12 +1865,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1889,7 +1880,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1910,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1929,12 +1920,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1944,12 +1935,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1959,7 +1950,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8620,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8649,7 +8640,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -8869,20 +8860,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1679呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,12 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +283,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1840,23 +1849,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>84000000</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>49822</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1910,23 +1915,19 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>84800000</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>50506</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -5434,7 +5435,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5444,12 +5445,12 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -5459,12 +5460,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -5474,7 +5475,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8631,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8640,7 +8641,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8860,20 +8861,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1679呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
+$8480万
+$50,506/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
--
--
-(待售)</t>
+$8400万
+$49,822/呎
+(26年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -9134,14 +9135,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>24</t>
@@ -9154,7 +9155,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9525,12 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 645呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
